--- a/data/trans_dic/P5_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P5_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con algún problema medioambiental importante en la zona de residencia</t>
+          <t>Hogares con algún problema medioambiental importante en la zona de residencia (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,5; 38,86</t>
+          <t>23,73; 38,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,91; 43,61</t>
+          <t>26,31; 43,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,19; 44,06</t>
+          <t>27,59; 44,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 11,15</t>
+          <t>3,49; 11,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,46; 39,38</t>
+          <t>25,23; 39,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,27; 45,66</t>
+          <t>29,51; 45,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,11; 46,84</t>
+          <t>30,23; 46,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 9,64</t>
+          <t>2,36; 9,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,61; 37,05</t>
+          <t>26,86; 37,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,69; 41,69</t>
+          <t>30,77; 41,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,78; 43,3</t>
+          <t>31,33; 43,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 8,75</t>
+          <t>3,52; 8,71</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,22; 29,56</t>
+          <t>18,22; 30,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,65; 37,46</t>
+          <t>24,29; 37,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,42; 36,96</t>
+          <t>24,51; 36,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,85; 20,67</t>
+          <t>11,71; 21,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,07; 39,69</t>
+          <t>27,03; 39,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,27; 36,23</t>
+          <t>23,62; 35,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,24; 40,92</t>
+          <t>29,22; 40,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,22; 14,0</t>
+          <t>6,99; 13,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,51; 33,29</t>
+          <t>24,41; 33,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,92; 34,28</t>
+          <t>25,69; 34,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,89; 36,76</t>
+          <t>28,99; 37,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,98; 15,3</t>
+          <t>10,01; 15,66</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,71; 32,02</t>
+          <t>19,61; 32,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,46; 39,88</t>
+          <t>25,15; 39,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,15; 42,83</t>
+          <t>29,18; 42,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,42; 57,11</t>
+          <t>15,0; 57,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,94; 27,36</t>
+          <t>15,12; 27,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,92; 42,14</t>
+          <t>27,16; 41,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,02; 43,21</t>
+          <t>30,48; 44,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,74; 24,48</t>
+          <t>13,32; 23,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,83; 27,8</t>
+          <t>19,11; 27,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,49; 39,41</t>
+          <t>28,19; 38,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,17; 41,82</t>
+          <t>31,79; 41,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,22; 41,81</t>
+          <t>16,13; 43,91</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,01; 37,14</t>
+          <t>25,02; 37,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,83; 58,24</t>
+          <t>44,18; 58,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,27; 45,49</t>
+          <t>31,88; 44,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,19; 36,82</t>
+          <t>23,99; 35,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,58; 30,16</t>
+          <t>19,3; 30,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,46; 56,84</t>
+          <t>43,11; 56,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,25; 46,01</t>
+          <t>33,52; 46,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,09; 41,5</t>
+          <t>29,25; 42,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,82; 32,52</t>
+          <t>23,67; 32,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,42; 54,95</t>
+          <t>46,09; 55,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,14; 43,85</t>
+          <t>34,28; 43,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,71; 37,08</t>
+          <t>28,29; 37,29</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,11; 31,24</t>
+          <t>25,01; 31,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,46; 41,73</t>
+          <t>34,63; 41,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,61; 38,46</t>
+          <t>31,7; 38,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,9; 31,97</t>
+          <t>17,06; 30,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,8; 31,05</t>
+          <t>24,75; 30,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,92; 41,77</t>
+          <t>34,62; 41,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,31; 40,94</t>
+          <t>33,9; 40,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,75; 19,85</t>
+          <t>14,7; 19,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,76; 30,3</t>
+          <t>25,67; 30,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35,81; 40,49</t>
+          <t>35,66; 40,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,97; 38,42</t>
+          <t>33,78; 38,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,67; 25,18</t>
+          <t>16,79; 24,46</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con algún problema medioambiental importante en la zona de residencia (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>33298</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33569</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>32440</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7627</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>38018</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>42151</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>40122</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>7186</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>71317</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>75720</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>72561</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>14813</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>24970; 40535</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25558; 41928</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24856; 40387</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4093; 13710</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>29840; 47156</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>33198; 51046</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>31644; 48364</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3313; 13784</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>60033; 82790</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>64499; 87387</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>61013; 84030</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>9076; 22449</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>29470</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>39351</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>46541</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>30143</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>47290</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>46076</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>61310</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>25772</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>76760</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>85426</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>107851</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>55915</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>22763; 37914</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>31332; 47873</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>37242; 55513</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>22312; 40315</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>38043; 56197</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>36500; 55501</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>51229; 71773</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>17831; 35336</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>64849; 89005</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>72830; 97201</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>94875; 121083</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>44611; 69785</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>27494</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33953</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>41594</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>53362</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>23567</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>40473</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>49041</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>33903</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>51061</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>74425</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>90635</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>87265</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>21153; 34945</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>26373; 41552</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>34011; 49625</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28554; 110417</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>17025; 31329</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>31718; 48709</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>40490; 58503</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>24684; 43786</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>42113; 61644</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>62476; 85729</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>79274; 104228</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>60603; 164982</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>51193</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>74535</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>62888</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>49937</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38772</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77443</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>62920</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>63357</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>89965</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>151978</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>125809</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>113294</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>41360; 62049</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>64501; 84985</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>52805; 74113</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>39954; 59333</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>30291; 48091</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>66788; 87843</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>53034; 73505</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>52732; 75912</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>76298; 103643</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>138702; 166201</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>111013; 140377</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>98137; 129330</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>141455</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>181408</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>183462</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>141069</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>147647</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>206142</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>213394</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>130218</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>289103</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>387550</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>396856</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>271288</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>125887; 158034</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>165150; 199619</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>166203; 201377</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>113404; 205224</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>130804; 162956</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>186550; 224109</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>193596; 231374</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>111905; 149274</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>264926; 311705</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>362249; 412672</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>369934; 423452</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>239320; 348796</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P5_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P5_R-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,73; 38,53</t>
+          <t>24,82; 39,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,31; 43,17</t>
+          <t>25,42; 42,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,59; 44,83</t>
+          <t>28,27; 44,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 11,69</t>
+          <t>3,38; 11,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,23; 39,87</t>
+          <t>25,55; 39,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,51; 45,37</t>
+          <t>29,65; 44,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,23; 46,2</t>
+          <t>30,23; 46,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 9,82</t>
+          <t>2,43; 10,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,86; 37,04</t>
+          <t>26,93; 36,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,77; 41,69</t>
+          <t>30,78; 42,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,33; 43,15</t>
+          <t>31,13; 42,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 8,71</t>
+          <t>3,54; 8,73</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,22; 30,34</t>
+          <t>17,62; 29,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,29; 37,12</t>
+          <t>24,42; 37,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,51; 36,54</t>
+          <t>24,79; 36,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,71; 21,16</t>
+          <t>11,64; 20,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,03; 39,93</t>
+          <t>27,89; 40,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,62; 35,91</t>
+          <t>23,57; 36,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,22; 40,94</t>
+          <t>29,75; 41,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,99; 13,86</t>
+          <t>7,16; 14,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,41; 33,5</t>
+          <t>24,93; 33,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,69; 34,28</t>
+          <t>26,14; 34,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,99; 37,0</t>
+          <t>28,72; 37,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,01; 15,66</t>
+          <t>9,8; 15,46</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,61; 32,4</t>
+          <t>19,33; 33,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,15; 39,63</t>
+          <t>25,6; 40,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,18; 42,58</t>
+          <t>28,6; 42,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,0; 57,99</t>
+          <t>14,74; 59,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,12; 27,83</t>
+          <t>15,27; 27,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,16; 41,71</t>
+          <t>27,21; 41,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,48; 44,04</t>
+          <t>30,21; 43,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,32; 23,63</t>
+          <t>13,75; 24,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,11; 27,97</t>
+          <t>19,18; 27,59</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,19; 38,68</t>
+          <t>28,22; 38,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,79; 41,79</t>
+          <t>31,14; 40,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,13; 43,91</t>
+          <t>16,37; 44,67</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,02; 37,53</t>
+          <t>25,35; 37,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,18; 58,21</t>
+          <t>44,0; 58,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,88; 44,74</t>
+          <t>32,37; 44,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,99; 35,63</t>
+          <t>24,4; 36,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,3; 30,64</t>
+          <t>19,38; 30,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,11; 56,69</t>
+          <t>42,38; 56,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,52; 46,46</t>
+          <t>34,17; 46,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,25; 42,1</t>
+          <t>28,68; 41,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,67; 32,16</t>
+          <t>24,01; 32,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46,09; 55,23</t>
+          <t>45,41; 55,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,28; 43,34</t>
+          <t>34,27; 43,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,29; 37,29</t>
+          <t>28,17; 36,99</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,01; 31,4</t>
+          <t>24,72; 31,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,63; 41,85</t>
+          <t>34,52; 41,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,7; 38,41</t>
+          <t>31,79; 38,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,06; 30,87</t>
+          <t>16,81; 32,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,75; 30,83</t>
+          <t>25,14; 31,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,62; 41,6</t>
+          <t>35,17; 41,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,9; 40,52</t>
+          <t>34,37; 40,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,7; 19,61</t>
+          <t>14,54; 19,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,67; 30,21</t>
+          <t>25,75; 30,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35,66; 40,63</t>
+          <t>35,53; 40,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,78; 38,66</t>
+          <t>33,94; 38,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,79; 24,46</t>
+          <t>16,66; 24,06</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24970; 40535</t>
+          <t>26113; 41573</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25558; 41928</t>
+          <t>24691; 40860</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24856; 40387</t>
+          <t>25465; 39860</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4093; 13710</t>
+          <t>3969; 13377</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>29840; 47156</t>
+          <t>30225; 46835</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33198; 51046</t>
+          <t>33358; 50391</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31644; 48364</t>
+          <t>31644; 48585</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3313; 13784</t>
+          <t>3418; 14349</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60033; 82790</t>
+          <t>60183; 81843</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64499; 87387</t>
+          <t>64514; 88099</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61013; 84030</t>
+          <t>60627; 82544</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9076; 22449</t>
+          <t>9122; 22496</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22763; 37914</t>
+          <t>22016; 37140</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31332; 47873</t>
+          <t>31503; 47956</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37242; 55513</t>
+          <t>37656; 56144</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22312; 40315</t>
+          <t>22182; 39140</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38043; 56197</t>
+          <t>39248; 56314</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36500; 55501</t>
+          <t>36426; 55680</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51229; 71773</t>
+          <t>52149; 72342</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17831; 35336</t>
+          <t>18256; 36794</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64849; 89005</t>
+          <t>66249; 88256</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72830; 97201</t>
+          <t>74125; 99120</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>94875; 121083</t>
+          <t>93993; 121339</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44611; 69785</t>
+          <t>43679; 68867</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21153; 34945</t>
+          <t>20846; 35850</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26373; 41552</t>
+          <t>26846; 42675</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34011; 49625</t>
+          <t>33338; 49217</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28554; 110417</t>
+          <t>28071; 113804</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17025; 31329</t>
+          <t>17191; 30747</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31718; 48709</t>
+          <t>31775; 48453</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40490; 58503</t>
+          <t>40129; 58442</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24684; 43786</t>
+          <t>25477; 44615</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>42113; 61644</t>
+          <t>42276; 60814</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62476; 85729</t>
+          <t>62535; 84779</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79274; 104228</t>
+          <t>77661; 101567</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>60603; 164982</t>
+          <t>61505; 167811</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41360; 62049</t>
+          <t>41915; 62566</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64501; 84985</t>
+          <t>64239; 84760</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52805; 74113</t>
+          <t>53616; 73913</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39954; 59333</t>
+          <t>40643; 60347</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30291; 48091</t>
+          <t>30413; 47782</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66788; 87843</t>
+          <t>65658; 87730</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53034; 73505</t>
+          <t>54054; 73746</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>52732; 75912</t>
+          <t>51707; 75437</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76298; 103643</t>
+          <t>77373; 105444</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>138702; 166201</t>
+          <t>136644; 167645</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>111013; 140377</t>
+          <t>110996; 140439</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>98137; 129330</t>
+          <t>97689; 128288</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>125887; 158034</t>
+          <t>124435; 156383</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>165150; 199619</t>
+          <t>164635; 199800</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>166203; 201377</t>
+          <t>166664; 201612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>113404; 205224</t>
+          <t>111726; 213673</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>130804; 162956</t>
+          <t>132896; 166042</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>186550; 224109</t>
+          <t>189494; 224900</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>193596; 231374</t>
+          <t>196243; 232148</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>111905; 149274</t>
+          <t>110621; 151459</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>264926; 311705</t>
+          <t>265693; 313158</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>362249; 412672</t>
+          <t>360875; 412380</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>369934; 423452</t>
+          <t>371768; 424218</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>239320; 348796</t>
+          <t>237586; 342996</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P5_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P5_R-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32,14%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37,47%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>38,33%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5,34%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>31,65%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>34,56%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>36,01%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,5%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>32,14%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>38,33%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,82; 39,51</t>
+          <t>25,46; 39,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,42; 42,07</t>
+          <t>30,27; 45,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,27; 44,25</t>
+          <t>30,11; 46,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 11,41</t>
+          <t>2,4; 10,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,55; 39,59</t>
+          <t>24,5; 38,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,65; 44,79</t>
+          <t>26,91; 43,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,23; 46,42</t>
+          <t>28,19; 44,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 10,22</t>
+          <t>3,44; 11,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,93; 36,62</t>
+          <t>26,61; 37,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,78; 42,03</t>
+          <t>30,69; 41,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,13; 42,38</t>
+          <t>31,78; 43,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 8,73</t>
+          <t>3,64; 9,02</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33,6%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29,81%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>34,97%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10,3%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>23,58%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>30,51%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>30,63%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15,82%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>33,6%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>29,81%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>34,97%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,62; 29,72</t>
+          <t>27,07; 39,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,42; 37,18</t>
+          <t>24,27; 36,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,79; 36,95</t>
+          <t>29,24; 40,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,64; 20,54</t>
+          <t>7,34; 14,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,89; 40,01</t>
+          <t>18,22; 29,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,57; 36,03</t>
+          <t>24,65; 37,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,75; 41,27</t>
+          <t>25,42; 36,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 14,43</t>
+          <t>12,02; 21,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,93; 33,22</t>
+          <t>24,51; 33,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,14; 34,96</t>
+          <t>25,92; 34,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,72; 37,08</t>
+          <t>28,89; 36,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,8; 15,46</t>
+          <t>10,12; 15,67</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20,93%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>34,66%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>36,92%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18,28%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>25,49%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>32,38%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>35,69%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28,03%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,93%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>34,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36,92%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,33; 33,24</t>
+          <t>14,94; 27,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,6; 40,7</t>
+          <t>27,92; 42,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,6; 42,23</t>
+          <t>30,02; 43,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,74; 59,77</t>
+          <t>13,48; 24,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,27; 27,31</t>
+          <t>19,71; 32,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,21; 41,49</t>
+          <t>25,46; 39,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,21; 43,99</t>
+          <t>29,15; 42,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,75; 24,08</t>
+          <t>13,74; 25,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,18; 27,59</t>
+          <t>18,83; 27,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,22; 38,25</t>
+          <t>28,49; 39,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,14; 40,72</t>
+          <t>32,17; 41,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,37; 44,67</t>
+          <t>14,85; 22,63</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24,7%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>49,98%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39,77%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>35,4%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>30,96%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>51,05%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>37,96%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29,98%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>24,7%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,98%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>39,77%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,35; 37,84</t>
+          <t>19,58; 30,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,0; 58,05</t>
+          <t>43,46; 56,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,37; 44,62</t>
+          <t>33,25; 46,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,4; 36,23</t>
+          <t>29,13; 41,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,38; 30,45</t>
+          <t>25,01; 37,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,38; 56,62</t>
+          <t>43,83; 58,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,17; 46,61</t>
+          <t>32,27; 45,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,68; 41,84</t>
+          <t>23,69; 35,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,01; 32,72</t>
+          <t>23,82; 32,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,41; 55,71</t>
+          <t>45,42; 54,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,27; 43,36</t>
+          <t>34,14; 43,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,17; 36,99</t>
+          <t>28,24; 36,86</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27,93%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>38,26%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>37,37%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>28,1%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>38,03%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>35,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>21,22%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>38,26%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>37,37%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,72; 31,07</t>
+          <t>24,8; 31,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,52; 41,89</t>
+          <t>34,92; 41,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,79; 38,46</t>
+          <t>34,31; 40,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,81; 32,14</t>
+          <t>15,07; 20,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,14; 31,41</t>
+          <t>25,11; 31,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,17; 41,74</t>
+          <t>34,46; 41,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,37; 40,65</t>
+          <t>31,61; 38,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,54; 19,9</t>
+          <t>16,01; 21,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,75; 30,35</t>
+          <t>25,76; 30,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35,53; 40,6</t>
+          <t>35,81; 40,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,94; 38,73</t>
+          <t>33,97; 38,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,66; 24,06</t>
+          <t>16,11; 19,86</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>38018</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42151</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>40122</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6719</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>33298</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>33569</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>32440</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7627</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>38018</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>42151</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>40122</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14813</t>
+          <t>14596</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26113; 41573</t>
+          <t>30113; 46577</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24691; 40860</t>
+          <t>34057; 51362</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25465; 39860</t>
+          <t>31520; 49030</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3969; 13377</t>
+          <t>3016; 12811</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30225; 46835</t>
+          <t>25775; 40880</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33358; 50391</t>
+          <t>26139; 42355</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31644; 48585</t>
+          <t>25396; 39690</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3418; 14349</t>
+          <t>4165; 13688</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60183; 81843</t>
+          <t>59470; 82809</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64514; 88099</t>
+          <t>64333; 87399</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60627; 82544</t>
+          <t>61892; 84337</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9122; 22496</t>
+          <t>8999; 22287</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>47290</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>46076</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>61310</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>24433</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>29470</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>39351</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>46541</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30143</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>47290</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>46076</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>61310</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25772</t>
+          <t>29881</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55915</t>
+          <t>54314</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22016; 37140</t>
+          <t>38099; 55859</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31503; 47956</t>
+          <t>37512; 55998</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37656; 56144</t>
+          <t>51257; 71739</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22182; 39140</t>
+          <t>17420; 33703</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39248; 56314</t>
+          <t>22765; 36938</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36426; 55680</t>
+          <t>31794; 48317</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52149; 72342</t>
+          <t>38614; 56155</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18256; 36794</t>
+          <t>22164; 38978</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66249; 88256</t>
+          <t>65130; 88443</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>74125; 99120</t>
+          <t>73493; 97193</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93993; 121339</t>
+          <t>94542; 120305</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43679; 68867</t>
+          <t>42665; 66077</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>41</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>23567</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>40473</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>49041</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>30777</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>27494</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>33953</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>41594</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>53362</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>23567</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>40473</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>49041</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33903</t>
+          <t>29244</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87265</t>
+          <t>60021</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20846; 35850</t>
+          <t>16817; 30796</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26846; 42675</t>
+          <t>32611; 49213</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33338; 49217</t>
+          <t>39886; 57403</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28071; 113804</t>
+          <t>22697; 41230</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17191; 30747</t>
+          <t>21254; 34531</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31775; 48453</t>
+          <t>26692; 41812</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40129; 58442</t>
+          <t>33979; 49914</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25477; 44615</t>
+          <t>21585; 39458</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>42276; 60814</t>
+          <t>41513; 61275</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62535; 84779</t>
+          <t>63143; 87348</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>77661; 101567</t>
+          <t>80232; 104298</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>61505; 167811</t>
+          <t>48309; 73638</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>71</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38772</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>77443</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>62920</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>59615</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>51193</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>74535</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>62888</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>49937</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>38772</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>77443</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>62920</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>63357</t>
+          <t>48629</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>113294</t>
+          <t>108244</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41915; 62566</t>
+          <t>30725; 47337</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64239; 84760</t>
+          <t>67344; 88067</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53616; 73913</t>
+          <t>52608; 72791</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40643; 60347</t>
+          <t>49068; 70103</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30413; 47782</t>
+          <t>41346; 61402</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65658; 87730</t>
+          <t>63998; 85030</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54054; 73746</t>
+          <t>53457; 75353</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51707; 75437</t>
+          <t>39483; 59416</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>77373; 105444</t>
+          <t>76758; 104799</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>136644; 167645</t>
+          <t>136697; 165375</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>110996; 140439</t>
+          <t>110555; 142031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>97689; 128288</t>
+          <t>94611; 123502</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>168</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>147647</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>206142</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>213394</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>121544</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>141455</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>181408</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>183462</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>141069</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>147647</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>206142</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>213394</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>130218</t>
+          <t>115631</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>271288</t>
+          <t>237175</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>124435; 156383</t>
+          <t>131055; 164091</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>164635; 199800</t>
+          <t>188165; 225055</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>166664; 201612</t>
+          <t>195913; 233758</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>111726; 213673</t>
+          <t>105481; 140487</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>132896; 166042</t>
+          <t>126371; 157231</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>189494; 224900</t>
+          <t>164366; 199035</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>196243; 232148</t>
+          <t>165689; 201641</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>110621; 151459</t>
+          <t>100715; 134229</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>265693; 313158</t>
+          <t>265826; 312670</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>360875; 412380</t>
+          <t>363763; 411236</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>371768; 424218</t>
+          <t>372034; 420792</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>237586; 342996</t>
+          <t>214098; 263885</t>
         </is>
       </c>
     </row>
